--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20211.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="50">
   <si>
     <t>Mat</t>
   </si>
@@ -85,37 +85,88 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>PERALTA</t>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>PATRICIO</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
   </si>
   <si>
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>GETSEMANI GUADALUPE</t>
+  </si>
+  <si>
     <t>NANCY PAOLA</t>
   </si>
   <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>MICHELLE GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
+  </si>
+  <si>
     <t>MARISOL</t>
   </si>
   <si>
-    <t>MICHELLE GUADALUPE</t>
+    <t>CRISTOPHER</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1072,16 +1123,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920201</v>
+        <v>21330051920197</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1090,67 +1141,67 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920288</v>
+        <v>21330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920327</v>
+        <v>21330051920201</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920243</v>
+        <v>21330051920250</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1159,7 +1210,145 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920288</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920289</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920243</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920262</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920327</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920337</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20211.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="60">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,12 @@
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>MATLATECATL</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
@@ -103,10 +109,16 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>PERALTA</t>
   </si>
   <si>
-    <t>HIDALGO</t>
+    <t>TEHUINTLE</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
@@ -124,13 +136,19 @@
     <t>TZOMPAXTLE</t>
   </si>
   <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
     <t>PORTILLA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ARCADIO</t>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
@@ -148,6 +166,12 @@
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>DULCE DANIELA</t>
+  </si>
+  <si>
+    <t>MARIA DEL PILAR</t>
+  </si>
+  <si>
     <t>GETSEMANI GUADALUPE</t>
   </si>
   <si>
@@ -157,10 +181,16 @@
     <t>ANDRES</t>
   </si>
   <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
     <t>MICHELLE GUADALUPE</t>
   </si>
   <si>
-    <t>ANA LILIANA</t>
+    <t>LUCERO</t>
   </si>
   <si>
     <t>MARISOL</t>
@@ -619,19 +649,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -762,16 +792,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>64.52</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -785,16 +818,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>69.44</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -808,16 +844,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -831,16 +870,19 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -854,16 +896,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -877,16 +922,19 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>88.45999999999999</v>
+      </c>
+      <c r="H7">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -942,13 +990,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>70.97</v>
+        <v>64.52</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -968,16 +1016,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>80.56</v>
+        <v>69.44</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -991,10 +1039,10 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>34</v>
@@ -1003,7 +1051,7 @@
         <v>79.06999999999999</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1020,16 +1068,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>88.37</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1046,13 +1094,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>87.5</v>
+        <v>83.33</v>
       </c>
       <c r="H6">
         <v>7.1</v>
@@ -1081,7 +1129,7 @@
         <v>88.45999999999999</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1091,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1129,10 +1177,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1141,7 +1189,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1152,10 +1200,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1164,7 +1212,7 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1175,10 +1223,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1187,21 +1235,21 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920250</v>
+        <v>21330051920240</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1210,73 +1258,73 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920288</v>
+        <v>21330051920241</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920289</v>
+        <v>21330051920250</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920243</v>
+        <v>21330051920288</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1284,39 +1332,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920262</v>
+        <v>21330051920289</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920327</v>
+        <v>21330051920298</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1325,21 +1373,21 @@
         <v>13</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920337</v>
+        <v>21330051920353</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1348,6 +1396,98 @@
         <v>14</v>
       </c>
       <c r="G11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920243</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920249</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920327</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920337</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20211.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20211.xlsx
@@ -1488,7 +1488,7 @@
         <v>14</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20211.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -85,118 +85,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>PATRICIO</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
     <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>MARIA DEL PILAR</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>NANCY PAOLA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>MICHELLE GUADALUPE</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
   </si>
 </sst>
 </file>
@@ -990,16 +885,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>64.52</v>
+        <v>83.87</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1016,13 +911,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>69.44</v>
+        <v>94.44</v>
       </c>
       <c r="H3">
         <v>7.6</v>
@@ -1042,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>79.06999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1068,16 +963,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>81.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1094,16 +989,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1120,16 +1015,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>88.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1171,16 +1066,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920197</v>
+        <v>21330051920201</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1190,305 +1085,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920386</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920201</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920240</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920241</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920250</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920288</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920289</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920298</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920353</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920243</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920249</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920327</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920337</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
